--- a/sample-due-database.xlsx
+++ b/sample-due-database.xlsx
@@ -398,17 +398,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I3"/>
-  <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -450,7 +439,7 @@
         <v>INV-1001</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E2" t="str">
         <v>2026-06-02</v>
